--- a/AAII_Financials/Quarterly/DELL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DELL_QTR_FIN.xlsx
@@ -656,494 +656,518 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="40" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46143</v>
+      </c>
+      <c r="F7" s="2">
         <v>46052</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45961</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45870</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45779</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45688</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45597</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45506</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45415</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45324</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45233</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45142</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45051</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44960</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44862</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44771</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44680</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44589</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44498</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44407</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44316</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44225</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44134</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44043</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43952</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43861</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43770</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43679</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43588</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43497</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43406</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43315</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43224</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43133</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>43042</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42951</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42860</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42769</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>46971000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>43842000</v>
+      </c>
+      <c r="F8" s="3">
         <v>33379000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>27005000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>29776000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>23378000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>23931000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>24366000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>25026000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>22244000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>22318000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>22251000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>22934000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>20922000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>25039000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>24721000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>26425000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>26116000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>22194000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>26424000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>24191000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>22590000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>18558000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>23482000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>22733000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>21897000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>24032000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>22844000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>23370000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>21908000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>23841000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>22482000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>22942000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>21356000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>21963000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>19556000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>19521000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>18000000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>20074000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>37116000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>35979000</v>
+      </c>
+      <c r="F9" s="3">
         <v>26618000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>21379000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>24281000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>18411000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>18214000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>18975000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>19609000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>17393000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>16770000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>17096000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>17520000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>15883000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>19283000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>19014000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>20986000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>20332000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>24005000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>20890000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>18716000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>17326000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>19688000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>16221000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>15577000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>15044000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>16348000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>15718000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>16044000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>15111000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>16732000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>16539000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>16819000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>15478000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>16071000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>14336000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>14553000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>13543000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>15543000</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>9855000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>7863000</v>
+      </c>
+      <c r="F10" s="3">
         <v>6761000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>5626000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>5495000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>4967000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>5717000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>5391000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>5417000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>4851000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>5548000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>5155000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>5414000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>5039000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>5756000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>5707000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>5439000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>5784000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>-1811000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>5534000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>5475000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>5264000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>-1130000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>7261000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>7156000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>6853000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>7684000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>7126000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>7326000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>6797000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>7109000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>5943000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>6123000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>5878000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>5892000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>5220000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>4968000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>4457000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>4531000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1184,124 +1208,132 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>960000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>943000</v>
+      </c>
+      <c r="F12" s="3">
         <v>761000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>719000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>757000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>775000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>762000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>702000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>735000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>763000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>691000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>691000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>692000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>687000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>739000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>677000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>626000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>681000</v>
       </c>
-      <c r="T12" s="3" t="s">
+      <c r="V12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>2066000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>697000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>619000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>1391000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>1360000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>1259000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>1265000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>1325000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>1262000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>1229000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>1176000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>1202000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>1140000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>1175000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>1087000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>2157000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AM12" s="3">
         <v>2118000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AN12" s="3">
         <v>2178000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AO12" s="3">
         <v>2248000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AP12" s="3">
         <v>1227000</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1416,91 +1448,97 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>260000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-404000</v>
+      </c>
+      <c r="F14" s="3">
         <v>60000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-58000</v>
       </c>
-      <c r="F14" s="3">
-        <v>200000</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
+        <v>221000</v>
+      </c>
+      <c r="I14" s="3">
         <v>-123000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-28000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>99000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>323000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>30000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>131000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>14000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>393000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>63000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>313000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>1000000</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>1581000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>-3960000</v>
       </c>
-      <c r="V14" s="3" t="s">
+      <c r="X14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W14" s="3" t="s">
+      <c r="Y14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>-338000</v>
       </c>
-      <c r="Z14" s="3" t="s">
+      <c r="AB14" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>10</v>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>10</v>
@@ -1517,68 +1555,74 @@
       <c r="AI14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AJ14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL14" s="3">
         <v>42000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AM14" s="3">
         <v>31000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AN14" s="3">
         <v>15000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AO14" s="3">
         <v>25000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AP14" s="3">
         <v>654000</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>754000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>758000</v>
+      </c>
+      <c r="F15" s="3">
         <v>483000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>756000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>762000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>738000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>449000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>765000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>784000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>800000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>425000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>822000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>831000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>809000</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1648,8 +1692,14 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1687,240 +1737,254 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>41325000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>39959000</v>
+      </c>
+      <c r="F17" s="3">
         <v>30167000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>24771000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>27799000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>22083000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>21644000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>22500000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>23306000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>21279000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>20413000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>20743000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>21405000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>19805000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>23744000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>23959000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>25155000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>24566000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>23203000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>21410000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>23174000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>21603000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>17840000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>22015000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>21597000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>21195000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>23315000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>22008000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>22851000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>21358000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>23510000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>22838000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>22955000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>21509000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>22032000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>19966000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>20186000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>19272000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>22079000</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5646000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>3883000</v>
+      </c>
+      <c r="F18" s="3">
         <v>3212000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>2234000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>1977000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>1295000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>2287000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>1866000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>1720000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>965000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>1905000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1508000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1529000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>1117000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>1295000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>762000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>1270000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>1550000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-1009000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>5014000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>1017000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>987000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>718000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>1467000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>1136000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>702000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>717000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>836000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>519000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>550000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>331000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-356000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>-13000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>-153000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>-69000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>-410000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>-665000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>-1272000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>-2005000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1961,588 +2025,620 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-145000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>29000</v>
+      </c>
+      <c r="F20" s="3">
         <v>31000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>27000</v>
       </c>
-      <c r="F20" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>-84000</v>
+      </c>
+      <c r="I20" s="3">
         <v>12000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>33000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>36000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>9000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>54000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>5000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>31000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>136000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>3000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>15000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-36000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-337000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-72000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>214000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-61000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>124000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>145000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-213000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>501000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>106000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>4000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-23000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>62000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>6000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>52000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-27000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>167000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>126000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>50000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>-75000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>53000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>25000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>246000</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6545000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>4612000</v>
+      </c>
+      <c r="F21" s="3">
         <v>3664000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>2963000</v>
       </c>
-      <c r="F21" s="3">
-        <v>2737000</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>2823000</v>
+      </c>
+      <c r="I21" s="3">
         <v>2021000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>2703000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>2595000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>2495000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>1711000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>2325000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>2299000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>2224000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>1923000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>2164000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1558000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1677000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>2204000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>35000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>6195000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>2381000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>2371000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>1878000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>3329000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>2457000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>2124000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>2256000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>2307000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>2079000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>2172000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>2323000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>1578000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>2085000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>1887000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>-4367000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>1652000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>1530000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>965000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>282000</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>400000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>391000</v>
+      </c>
+      <c r="F22" s="3">
         <v>411000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>396000</v>
       </c>
-      <c r="F22" s="3">
-        <v>399000</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
+        <v>400000</v>
+      </c>
+      <c r="I22" s="3">
         <v>354000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>343000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>321000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>387000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>343000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>373000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>371000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>352000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>405000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>387000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>272000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>298000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>265000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>67000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>406000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>416000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>433000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>197000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>566000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>617000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>672000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>630000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>654000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>692000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>699000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>658000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>612000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>622000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>596000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>604000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>607000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>598000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AO22" s="3">
         <v>597000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AP22" s="3">
         <v>651000</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5131000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3948000</v>
+      </c>
+      <c r="F23" s="3">
         <v>2799000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>1941000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>1440000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>1083000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1972000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1445000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>1039000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>592000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1488000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1180000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>714000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>705000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>923000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>454000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>635000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>1213000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-862000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>4547000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>725000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>699000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>308000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>1402000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>500000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>136000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>91000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>159000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-111000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-143000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-275000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-995000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>-468000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>-623000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>-623000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>-1092000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>-1210000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>-1844000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>-2410000</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>998000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>510000</v>
+      </c>
+      <c r="F24" s="3">
         <v>540000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>393000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>276000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>118000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>440000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>275000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>157000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-400000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>153000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>176000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>259000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>127000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>317000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>213000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>129000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>144000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-98000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>864000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>96000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>40000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>225000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>521000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-599000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-46000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-325000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>7000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>-4343000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-472000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>12000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>-100000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>-7000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>-85000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>-490000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>-241000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>-471000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>-641000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>-996000</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2657,240 +2753,258 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4133000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>3438000</v>
+      </c>
+      <c r="F26" s="3">
         <v>2259000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>1548000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>1164000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>965000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1532000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>1170000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>882000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>992000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1335000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1004000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>455000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>578000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>606000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>241000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>506000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>1069000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-764000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>3683000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>629000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>659000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>83000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>881000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>1099000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>182000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>416000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>152000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>4232000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>329000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-287000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-895000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-461000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>-538000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>-133000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>-851000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>-739000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>-1203000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>-1414000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4133000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>3438000</v>
+      </c>
+      <c r="F27" s="3">
         <v>2259000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>1548000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>1164000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>965000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1533000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>1175000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>887000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>997000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1337000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1006000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>462000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>583000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>614000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>245000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>511000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>1072000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-613000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>3685000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>631000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>660000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>226000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>832000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>1048000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>143000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>408000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>99000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>3416000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>293000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-299000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-876000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-499000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>-636000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>-100000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>-846000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>-732000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>-1171000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>-1380000</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3005,8 +3119,14 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3059,70 +3179,76 @@
         <v>0</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>615000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="W29" s="3">
         <v>158000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="X29" s="3">
         <v>200000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="Y29" s="3">
         <v>227000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Z29" s="3">
         <v>1001000</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>400000</v>
       </c>
-      <c r="AD29" s="3" t="s">
+      <c r="AF29" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF29" s="3">
-        <v>0</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>10</v>
+      <c r="AH29" s="3">
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL29" s="3">
         <v>300000</v>
       </c>
-      <c r="AK29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL29" s="3">
-        <v>0</v>
-      </c>
       <c r="AM29" s="3">
         <v>0</v>
       </c>
       <c r="AN29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="3">
         <v>1144000</v>
       </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3237,8 +3363,14 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3353,240 +3485,258 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-31000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-27000</v>
       </c>
-      <c r="F32" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>84000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-12000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-33000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-36000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-9000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-54000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-5000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-31000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-136000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-3000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>36000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>337000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>72000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-214000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>61000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-124000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-145000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>213000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-501000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>19000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-106000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>23000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-62000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-52000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>27000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-167000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-126000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-50000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>75000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-53000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>-246000</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4133000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>3438000</v>
+      </c>
+      <c r="F33" s="3">
         <v>2259000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>1548000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>1164000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>965000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1533000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>1175000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>887000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>997000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1337000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1006000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>462000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>583000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>614000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>245000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>511000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>1072000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>2000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>3843000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>831000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>887000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>1227000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>832000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>1048000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>143000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>408000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>499000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>3416000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>293000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-299000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-876000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-499000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>-636000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>200000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>-846000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>-732000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>-1171000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>-236000</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3701,245 +3851,263 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4133000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>3438000</v>
+      </c>
+      <c r="F35" s="3">
         <v>2259000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>1548000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>1164000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>965000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1533000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>1175000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>887000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>997000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1337000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1006000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>462000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>583000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>614000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>245000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>511000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>1072000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>2000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>3843000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>831000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>887000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>1227000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>832000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>1048000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>143000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>408000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>499000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>3416000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>293000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-299000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-876000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-499000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>-636000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>200000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>-846000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>-732000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>-1171000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>-236000</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46143</v>
+      </c>
+      <c r="F38" s="2">
         <v>46052</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45961</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45870</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45779</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45688</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45597</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45506</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45415</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45324</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45233</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45142</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45051</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44960</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44862</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44771</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44680</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44589</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44498</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44407</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44316</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44225</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44134</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44043</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43952</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43861</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43770</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43679</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43588</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43497</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43406</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43315</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43224</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43133</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>43042</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42951</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42860</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42769</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3980,8 +4148,10 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4022,169 +4192,177 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11569000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>11578000</v>
+      </c>
+      <c r="F41" s="3">
         <v>11528000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>9569000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>8145000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>7700000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>3633000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>5225000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>4550000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>5830000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>7366000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>8298000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>8364000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>7631000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>8607000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>4909000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>5507000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>6654000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>9477000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>22406000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>11719000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>14244000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>9508000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>11304000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>11221000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>12229000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>9302000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>8555000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>9193000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>9040000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>9676000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>15152000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>15312000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>15324000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>13942000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>11706000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>9213000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>9554000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>9474000</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F42" s="3">
         <v>5000</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>1000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>4000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>60000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>123000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>198000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>288000</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>205000</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4231,843 +4409,891 @@
         <v>0</v>
       </c>
       <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
         <v>2322000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>2504000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AK42" s="3">
         <v>2402000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AL42" s="3">
         <v>2187000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AM42" s="3">
         <v>2008000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AN42" s="3">
         <v>2015000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AO42" s="3">
         <v>1620000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AP42" s="3">
         <v>1975000</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>22918000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>25854000</v>
+      </c>
+      <c r="F43" s="3">
         <v>17585000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>11721000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>15023000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>13635000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>10298000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>11189000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>11391000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>8563000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>9343000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>10106000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>10755000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>9783000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>17763000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>16346000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>18291000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>16633000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>18001000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>19147000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>17869000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>15889000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>15879000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>16249000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>16498000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>15549000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>17379000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>16036000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>16059000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>14794000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>16769000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>15247000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>15341000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>14523000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>15640000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>12832000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>13189000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>12089000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AP43" s="3">
         <v>12642000</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>21290000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>15052000</v>
+      </c>
+      <c r="F44" s="3">
         <v>10437000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>6949000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>7211000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>7415000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>6716000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>6652000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>5953000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>4782000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>3622000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>3381000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>3584000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>4016000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>4776000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>6172000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>5883000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>6277000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>5898000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>5442000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>4223000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>3828000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>3403000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>3393000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>3602000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>3616000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>3281000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>3257000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>3135000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>3360000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>3649000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>3793000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>3642000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>2933000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>2678000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>2582000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>2594000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>2466000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AP44" s="3">
         <v>2538000</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>11964000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>9154000</v>
+      </c>
+      <c r="F45" s="3">
         <v>9037000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>8436000</v>
       </c>
-      <c r="F45" s="3">
-        <v>8283000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>8640000</v>
-      </c>
       <c r="H45" s="3">
+        <v>8429000</v>
+      </c>
+      <c r="I45" s="3">
+        <v>8793000</v>
+      </c>
+      <c r="J45" s="3">
         <v>9710000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>9786000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>9678000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>10467000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>9997000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>10517000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>11208000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>10453000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>11205000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>11360000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>12581000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>11812000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>11657000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>10184000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>9744000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>8378000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>14777000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>7668000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>9769000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>9537000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>6906000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>6924000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>6929000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>6461000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>6044000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>6445000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>6326000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>6049000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>5881000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>5397000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>5194000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>4655000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>4144000</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>80547000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>70607000</v>
+      </c>
+      <c r="F46" s="3">
         <v>57602000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>43102000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>45512000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>42925000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>36229000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>38035000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>37543000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>34627000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>35984000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>36987000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>38999000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>37392000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>42351000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>38787000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>42262000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>41376000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>45033000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>57179000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>43555000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>42339000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>43567000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>38614000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>41090000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>40931000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>36868000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>34772000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>35316000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>33655000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>36138000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>42959000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>43125000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>41231000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>40328000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>34525000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>32205000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>30384000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>30773000</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2721000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>2518000</v>
+      </c>
+      <c r="F47" s="3">
         <v>1767000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>1809000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>1646000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>1649000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>1536000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>1352000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>1331000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>1327000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1316000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>1351000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1399000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>1471000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>7156000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>7193000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>6970000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>7266000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>7361000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>7097000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>7205000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>6931000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>6673000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>7029000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>6451000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>5684000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>5712000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>5303000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>5118000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>4913000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>5229000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>6918000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>7679000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>7742000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AL47" s="3">
         <v>7887000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AM47" s="3">
         <v>7590000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AN47" s="3">
         <v>7221000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AO47" s="3">
         <v>6513000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AP47" s="3">
         <v>6453000</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4964000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>4875000</v>
+      </c>
+      <c r="F48" s="3">
         <v>4857000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>4863000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>7157000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>7078000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>4811000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>7027000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>7016000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>6880000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>7139000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>6933000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>6968000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>6995000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>6934000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>6574000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>6556000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>6353000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>6286000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>8878000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>8705000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>8645000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>5954000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>8523000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>8167000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>7845000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>7835000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>7539000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>7198000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>7032000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>5259000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>5228000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>5240000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>5303000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>5390000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>5378000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>5400000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>5438000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>5653000</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>23795000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>23943000</v>
+      </c>
+      <c r="F49" s="3">
         <v>24606000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>23986000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>24084000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>24183000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>24731000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>24390000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>25028000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>25178000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>26047000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>25523000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>25700000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>25930000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>26144000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>26094000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>26477000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>26815000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>27231000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>53020000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>53755000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>54568000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>29143000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>55900000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>56708000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>57075000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>59798000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>60862000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>59717000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>60963000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>62359000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>63438000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>64712000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>66393000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>68185000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>69176000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>70987000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>72213000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AP49" s="3">
         <v>73963000</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5182,8 +5408,14 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5298,124 +5530,136 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4559000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>4526000</v>
+      </c>
+      <c r="F52" s="3">
         <v>588000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>4644000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>4706000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>4992000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>319000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>5298000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>5645000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>6237000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>692000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>4496000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>4502000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>4548000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>7026000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>6524000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>6510000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>6596000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>6824000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>9503000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>9458000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>9269000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>47157000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>8882000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>8860000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>8701000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>8648000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>8338000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>8171000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>3329000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>2835000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>2698000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>2625000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>2548000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>2403000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>1725000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>1681000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>1492000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>1364000</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5530,124 +5774,136 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>127393000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>114913000</v>
+      </c>
+      <c r="F54" s="3">
         <v>101286000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>87479000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>89176000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>86869000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>79746000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>81951000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>82687000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>80190000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>82126000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>83264000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>85658000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>84094000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>89611000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>85172000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>88775000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>88406000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>92735000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>135677000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>122678000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>121752000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>123415000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>118948000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>121276000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>120236000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>118861000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>116814000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>115520000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>109892000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>111820000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>121241000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>123381000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>123217000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>124193000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>118394000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>117494000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>116040000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>118206000</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5688,8 +5944,10 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5730,704 +5988,742 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>49723000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>45261000</v>
+      </c>
+      <c r="F57" s="3">
         <v>33630000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>23794000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>27463000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>25349000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>20832000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>23400000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>24095000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>20586000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>19226000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>20724000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>21221000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>18390000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>18598000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>22507000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>25339000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>25585000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>27143000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>26772000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>23029000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>21545000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>21572000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>19792000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>19500000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>18432000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>20065000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>19443000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>19411000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>18097000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>19213000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>19748000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>20853000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>18534000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>18334000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>16711000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>16916000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>15064000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>14422000</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8734000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>7801000</v>
+      </c>
+      <c r="F58" s="3">
         <v>8236000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>7641000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>7395000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>5084000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>5441000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>5854000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>6957000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>6340000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>7235000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>6744000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>7216000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>5738000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>6573000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>6767000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>6647000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>5925000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>5823000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>16280000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>6427000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>8748000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>6357000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>6536000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>10345000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>8375000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>7737000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>7664000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>5949000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>4884000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>4320000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>8150000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>9144000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>7133000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>7873000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>6235000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>7686000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>4842000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AP58" s="3">
         <v>6329000</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>14840000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>13291000</v>
+      </c>
+      <c r="F59" s="3">
         <v>13430000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>12703000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>13878000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>14091000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>13925000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>14064000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>14871000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>15049000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>15800000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>15265000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>16233000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>15575000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>26483000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>22733000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>22803000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>21549000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>23253000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>26650000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>26027000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>24563000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>26203000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>23974000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>24443000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>23204000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>24654000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>21948000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>21660000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>20498000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>21439000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>19685000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>19181000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>18447000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>19632000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>17796000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>17524000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>16730000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>17384000</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>83703000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>74598000</v>
+      </c>
+      <c r="F60" s="3">
         <v>63269000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>50516000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>54862000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>50422000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>46527000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>49500000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>52033000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>47734000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>48354000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>48877000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>50942000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>46825000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>51654000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>52007000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>54789000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>53059000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>56219000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>69702000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>55483000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>54856000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>54132000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>50302000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>54288000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>50011000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>52456000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>49055000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>47020000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>43479000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>44972000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>47583000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>49178000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>44114000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>45839000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>40742000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>42126000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>36636000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>38135000</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>23137000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>20620000</v>
+      </c>
+      <c r="F61" s="3">
         <v>20604000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>20621000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>17932000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>20424000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>16392000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>16419000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>14994000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>15916000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>15987000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>16478000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>16552000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>18703000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>23015000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>20562000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>20287000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>21197000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>21131000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>31699000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>37167000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>37935000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>32865000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>43325000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>43608000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>48353000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>44319000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>44727000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>45973000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>48640000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>49201000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>40507000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>40414000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>44770000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>43998000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>45416000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>41374000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>44948000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>43061000</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3610000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3337000</v>
+      </c>
+      <c r="F62" s="3">
         <v>1422000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>2728000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>2535000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>2516000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>971000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>2209000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>2147000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>2147000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>761000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>2386000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>2461000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>2397000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>17967000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>15971000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>16454000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>16505000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>16965000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>20082000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>20085000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>19817000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>31966000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>18855000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>18212000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>18191000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>18302000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>18221000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>18408000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>17660000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>17393000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>16631000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>16522000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>16509000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>16487000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>16648000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>16725000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>16765000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>17770000</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6542,8 +6838,14 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6658,8 +6960,14 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6774,124 +7082,136 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>128820000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>116317000</v>
+      </c>
+      <c r="F66" s="3">
         <v>103756000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>90099000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>91942000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>89893000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>81133000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>84141000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>85484000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>82913000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>84258000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>85834000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>88335000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>87018000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>92733000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>88641000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>91635000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>90868000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>94420000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>126723000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>117853000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>117707000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>120464000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>117538000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>121085000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>121409000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>119806000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>117684000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>116945000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>114582000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>116389000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>111554000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>112762000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>111888000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>112090000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>108513000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>106214000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>104207000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>104732000</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6932,8 +7252,10 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7048,8 +7370,14 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7164,8 +7492,14 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7227,61 +7561,67 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
         <v>558000</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Z70" s="3">
         <v>472000</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="AA70" s="3">
         <v>527000</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AB70" s="3">
         <v>610000</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AC70" s="3">
         <v>441000</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AD70" s="3">
         <v>629000</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AE70" s="3">
         <v>934000</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AF70" s="3">
         <v>1024000</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AG70" s="3">
         <v>1774000</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AH70" s="3">
         <v>1196000</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AI70" s="3">
         <v>2095000</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AJ70" s="3">
         <v>2056000</v>
       </c>
-      <c r="AI70" s="3">
+      <c r="AK70" s="3">
         <v>844000</v>
       </c>
-      <c r="AJ70" s="3">
+      <c r="AL70" s="3">
         <v>384000</v>
       </c>
-      <c r="AK70" s="3">
+      <c r="AM70" s="3">
         <v>362000</v>
       </c>
-      <c r="AL70" s="3">
+      <c r="AN70" s="3">
         <v>333000</v>
       </c>
-      <c r="AM70" s="3">
+      <c r="AO70" s="3">
         <v>301000</v>
       </c>
-      <c r="AN70" s="3">
+      <c r="AP70" s="3">
         <v>231000</v>
       </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7396,124 +7736,136 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10065000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>6343000</v>
+      </c>
+      <c r="F72" s="3">
         <v>3325000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1420000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>231000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-567000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-1160000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-2669000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-3478000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-4001000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-4453000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-5519000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-6249000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-6430000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-6732000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-7102000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-7106000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-7369000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-8188000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-8190000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-12033000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-12864000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-13751000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-14978000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-15810000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-16858000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-16891000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-17299000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-17775000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-21053000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-21349000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-8813000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>-7937000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>-7438000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>-6860000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>-8742000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>-7805000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>-6859000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>-5609000</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7628,8 +7980,14 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7744,8 +8102,14 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7860,124 +8224,136 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1427000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-1404000</v>
+      </c>
+      <c r="F76" s="3">
         <v>-2470000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-2620000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-2766000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-3024000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-1482000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-2285000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-2894000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-2822000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-2227000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-2664000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-2772000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-3023000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-3122000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-3469000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-2860000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-2462000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>-1685000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>8954000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>4825000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>3487000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>2479000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>883000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>-419000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>-1614000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>-1574000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>-1804000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>-2449000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>-6464000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>-5765000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>7592000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>8563000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>10485000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>11719000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>9519000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>10947000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>11532000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>13243000</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8092,245 +8468,263 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46143</v>
+      </c>
+      <c r="F80" s="2">
         <v>46052</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45961</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45870</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45779</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45688</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45597</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45506</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45415</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45324</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45233</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45142</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45051</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44960</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44862</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44771</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44680</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44589</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44498</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44407</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44316</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44225</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44134</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44043</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43952</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43861</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43770</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43679</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43588</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43497</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43406</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43315</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43224</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43133</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>43042</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42951</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42860</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42769</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4133000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>3438000</v>
+      </c>
+      <c r="F81" s="3">
         <v>2259000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>1548000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>1164000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>965000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1533000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>1175000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>887000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>997000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1337000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1006000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>462000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>583000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>614000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>245000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>511000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>1072000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>2000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>3843000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>831000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>887000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>1227000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>832000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>1048000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>143000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>408000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>499000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>3416000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>293000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-299000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-876000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-499000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>-636000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>200000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>-846000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>-732000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>-1171000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>-236000</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8371,124 +8765,132 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>637000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>612000</v>
+      </c>
+      <c r="F83" s="3">
         <v>286000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>597000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>616000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>632000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>205000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>617000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>623000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>609000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>299000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>587000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>500000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>483000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>854000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>832000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>744000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>726000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>830000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>1242000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>1240000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>1239000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>1373000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>1361000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>1340000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>1316000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>1535000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>1494000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>1498000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>1616000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>1940000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>1961000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>1931000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>1914000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>2143000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>2137000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>2142000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>2212000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>2041000</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8603,8 +9005,14 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8719,8 +9127,14 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8835,8 +9249,14 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8951,8 +9371,14 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9067,124 +9493,136 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2225000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>4081000</v>
+      </c>
+      <c r="F89" s="3">
         <v>4674000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1172000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>2543000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>2796000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>585000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1553000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1340000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1043000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1533000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>2152000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>3214000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1777000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>2714000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>396000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>724000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-269000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>3093000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>3251000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1725000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>2238000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>5877000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>2994000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>3332000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-796000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>3508000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>1821000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>3280000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>682000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>2366000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>833000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>2633000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>1159000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>3099000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>1639000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>1820000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>285000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>740000</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9225,124 +9663,132 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1239000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-963000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-721000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-669000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-675000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-568000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-735000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-639000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-682000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-596000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-727000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-704000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-624000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-701000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-759000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-747000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-807000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-690000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-740000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-799000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-622000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-625000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-498000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-480000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-545000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-559000</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
       <c r="AD91" s="3">
         <v>0</v>
       </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-21000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-20000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-282000</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9457,8 +9903,14 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9573,124 +10025,136 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1337000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1067000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-695000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-617000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-655000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-88000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-678000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-524000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-557000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-456000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-669000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-825000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-605000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-684000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-796000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-730000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-778000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-720000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-747000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>3241000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-669000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-519000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-486000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>1435000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-924000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-485000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-704000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-2699000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-825000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-458000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>3610000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-59000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-13000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-149000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-885000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-700000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-1341000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>51000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>6803000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9731,65 +10195,67 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>405000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>464000</v>
+      </c>
+      <c r="F96" s="3">
         <v>346000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>351000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>366000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>396000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>311000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>312000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>316000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>336000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>261000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>266000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>269000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>276000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-236000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-238000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-242000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-248000</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -9847,8 +10313,14 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9963,8 +10435,14 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10079,8 +10557,14 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10195,352 +10679,376 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-882000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-2954000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-2093000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>857000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1465000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>1237000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1391000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-315000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-2032000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-2077000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1819000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-1446000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1827000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-2002000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>1513000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-386000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-1046000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-1706000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-15581000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>4283000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-3673000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-1638000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-2467000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-4310000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-3437000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>4264000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-2004000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>322000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-2203000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-719000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-11485000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-857000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-2530000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>543000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-122000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>1600000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-888000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-187000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>-6902000</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>89000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-101000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>19000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-42000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-55000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>14000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-83000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-59000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-58000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>239000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-149000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-83000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-111000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>239000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-149000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-83000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-111000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-52000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-33000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-16000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-5000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>103000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-15000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>84000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-136000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>10000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-38000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-26000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-36000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>73000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-46000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>-130000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-86000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>128000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>54000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AP101" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>47000</v>
+      </c>
+      <c r="F102" s="3">
         <v>1973000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1442000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>438000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>4034000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-1585000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>733000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1291000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1545000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-941000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-202000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>723000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-967000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>3670000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-869000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-1183000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-2806000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-13287000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>10742000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-2633000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>76000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>3027000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>104000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-945000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>2847000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>810000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-594000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>226000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-531000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-5436000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-129000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-40000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>1467000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>2220000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>2540000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>-357000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>143000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>570000</v>
       </c>
     </row>
